--- a/data/productos.xlsx
+++ b/data/productos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Berni\Desktop\imed-ortopedia\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B809BDDB-AB5E-4263-B190-C46D71764FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0591002F-8AFA-4293-9F6D-852C1220FD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13275" yWindow="1980" windowWidth="17040" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13275" yWindow="1980" windowWidth="26655" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="productos" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="1823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4360" uniqueCount="1863">
   <si>
     <t>slug</t>
   </si>
@@ -5634,6 +5634,136 @@
   </si>
   <si>
     <t>/products/aspen/almohadilla-aspen-rectangular.jpg</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Tipo Poliform Liso</t>
+  </si>
+  <si>
+    <t>Plantillas</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-poliform-liso.jpg</t>
+  </si>
+  <si>
+    <t>Taller, plantillas ortopedia</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-poliform-perforado</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Tipo Poliform Perforado</t>
+  </si>
+  <si>
+    <t>Nuestras plantillas ortopédicas personalizadas están diseñadas para adaptarse exactamente a la forma y necesidades de cada pie, brindando mayor confort, estabilidad y alivio al caminar.
+Realizamos una evaluación personalizada para crear una solución única que ayude a mejorar tu pisada.
+Trabajamos con materiales de alta calidad y tecnología especializada para garantizar durabilidad, comodidad y un ajuste preciso tanto para uso diario como deportivo.
+Ideales para tratar:
+Pie plano
+Fascitis plantar
+Dolor de talón
+Metatarsalgia
+Problemas posturales
+Fatiga al caminar o permanecer de pie
+Cada plantilla se fabrica a medida, pensando en tu bienestar y calidad de vida.</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Tipo Evasote Liso</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Tipo Evasote Perforado</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Vip Ecocuero (Tipo Valenti Valenti)</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Camuflada Verde</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Camuflada Blanco y Negro</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Camuflada Azul y Negro</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Multicolor</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Tipo Poliform Perforado Azul</t>
+  </si>
+  <si>
+    <t>Plantilla Ortopédica Plastazote Ottobock Alemán Perforado</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-evasote-liso</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-evasote-perforado</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-ecocuero</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-camuflada-verde</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-camuflada-negro</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-camuflada-azul</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-multicolor</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-poliform-perforado-azul</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-plastazote-aleman</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas-poliform-liso</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-evasote-liso.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-evasote-perforado.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-ecocuero.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-camuflada-verde.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-camuflada-negro.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-camuflada-azul.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-multicolor.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-poliform-perforado-azul.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-plastazote-aleman.jpg</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-poliform-perforado.jpg</t>
+  </si>
+  <si>
+    <t>plantillas-ortopedicas</t>
+  </si>
+  <si>
+    <t>Plantillas Ortopédicas a Medida</t>
+  </si>
+  <si>
+    <t>/products/plantillas/plantillas-ortopedicas.jpg</t>
   </si>
 </sst>
 </file>
@@ -6013,9 +6143,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M472"/>
+  <dimension ref="A1:M484"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="32.25" customWidth="1"/>
     <col min="4" max="4" width="22.125" customWidth="1"/>
     <col min="5" max="5" width="52.75" customWidth="1"/>
   </cols>
@@ -10237,7 +10368,7 @@
         <v>20</v>
       </c>
       <c r="L103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -25369,6 +25500,498 @@
         <v>1</v>
       </c>
       <c r="M472" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F473">
+        <v>0</v>
+      </c>
+      <c r="G473">
+        <v>0</v>
+      </c>
+      <c r="H473" t="s">
+        <v>17</v>
+      </c>
+      <c r="I473" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J473" t="s">
+        <v>1826</v>
+      </c>
+      <c r="K473" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L473" t="b">
+        <v>0</v>
+      </c>
+      <c r="M473" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C474" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D474" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E474" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F474">
+        <v>0</v>
+      </c>
+      <c r="G474">
+        <v>0</v>
+      </c>
+      <c r="H474" t="s">
+        <v>17</v>
+      </c>
+      <c r="I474" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J474" t="s">
+        <v>1850</v>
+      </c>
+      <c r="K474" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L474" t="b">
+        <v>0</v>
+      </c>
+      <c r="M474" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D475" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E475" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F475">
+        <v>0</v>
+      </c>
+      <c r="G475">
+        <v>0</v>
+      </c>
+      <c r="H475" t="s">
+        <v>17</v>
+      </c>
+      <c r="I475" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J475" t="s">
+        <v>1851</v>
+      </c>
+      <c r="K475" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L475" t="b">
+        <v>0</v>
+      </c>
+      <c r="M475" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C476" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D476" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E476" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F476">
+        <v>0</v>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+      <c r="H476" t="s">
+        <v>17</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J476" t="s">
+        <v>1852</v>
+      </c>
+      <c r="K476" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L476" t="b">
+        <v>0</v>
+      </c>
+      <c r="M476" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1834</v>
+      </c>
+      <c r="C477" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D477" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E477" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F477">
+        <v>0</v>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+      <c r="H477" t="s">
+        <v>17</v>
+      </c>
+      <c r="I477" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J477" t="s">
+        <v>1853</v>
+      </c>
+      <c r="K477" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L477" t="b">
+        <v>0</v>
+      </c>
+      <c r="M477" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C478" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D478" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E478" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F478">
+        <v>0</v>
+      </c>
+      <c r="G478">
+        <v>0</v>
+      </c>
+      <c r="H478" t="s">
+        <v>17</v>
+      </c>
+      <c r="I478" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J478" t="s">
+        <v>1854</v>
+      </c>
+      <c r="K478" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L478" t="b">
+        <v>0</v>
+      </c>
+      <c r="M478" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C479" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E479" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F479">
+        <v>0</v>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+      <c r="H479" t="s">
+        <v>17</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J479" t="s">
+        <v>1855</v>
+      </c>
+      <c r="K479" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L479" t="b">
+        <v>0</v>
+      </c>
+      <c r="M479" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C480" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D480" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E480" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F480">
+        <v>0</v>
+      </c>
+      <c r="G480">
+        <v>0</v>
+      </c>
+      <c r="H480" t="s">
+        <v>17</v>
+      </c>
+      <c r="I480" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J480" t="s">
+        <v>1856</v>
+      </c>
+      <c r="K480" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L480" t="b">
+        <v>0</v>
+      </c>
+      <c r="M480" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C481" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D481" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E481" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F481">
+        <v>0</v>
+      </c>
+      <c r="G481">
+        <v>0</v>
+      </c>
+      <c r="H481" t="s">
+        <v>17</v>
+      </c>
+      <c r="I481" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J481" t="s">
+        <v>1857</v>
+      </c>
+      <c r="K481" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L481" t="b">
+        <v>0</v>
+      </c>
+      <c r="M481" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C482" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D482" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E482" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F482">
+        <v>0</v>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+      <c r="H482" t="s">
+        <v>17</v>
+      </c>
+      <c r="I482" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J482" t="s">
+        <v>1858</v>
+      </c>
+      <c r="K482" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L482" t="b">
+        <v>0</v>
+      </c>
+      <c r="M482" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C483" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D483" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E483" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F483">
+        <v>0</v>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+      <c r="H483" t="s">
+        <v>17</v>
+      </c>
+      <c r="I483" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J483" t="s">
+        <v>1859</v>
+      </c>
+      <c r="K483" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L483" t="b">
+        <v>0</v>
+      </c>
+      <c r="M483" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>1830</v>
+      </c>
+      <c r="D484" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E484" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F484">
+        <v>0</v>
+      </c>
+      <c r="G484">
+        <v>0</v>
+      </c>
+      <c r="H484" t="s">
+        <v>17</v>
+      </c>
+      <c r="I484" t="s">
+        <v>1825</v>
+      </c>
+      <c r="J484" t="s">
+        <v>1862</v>
+      </c>
+      <c r="K484" t="s">
+        <v>1827</v>
+      </c>
+      <c r="L484" t="b">
+        <v>1</v>
+      </c>
+      <c r="M484" t="b">
         <v>1</v>
       </c>
     </row>
